--- a/exports/JSWENERGY_full_report.xlsx
+++ b/exports/JSWENERGY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44606.55208333334</v>
+        <v>44607.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>324.25</v>
+        <v>311.7</v>
       </c>
       <c r="I2" t="n">
         <v>314.7630066172184</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K2" t="n">
-        <v>4.82</v>
+        <v>0.76</v>
       </c>
       <c r="L2" t="n">
         <v>5.93</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.04</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>314.45</v>
+        <v>324.65</v>
       </c>
       <c r="I3" t="n">
         <v>316.110804119584</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.88</v>
+        <v>-4.15</v>
       </c>
       <c r="L3" t="n">
         <v>13.25</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.65</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.38541666666</v>
+        <v>44664.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>329.75</v>
+        <v>328.7</v>
       </c>
       <c r="I4" t="n">
         <v>328.775499149137</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="L4" t="n">
         <v>3.28</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.52</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44701.55208333334</v>
+        <v>44704.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>293.7</v>
+        <v>316.3</v>
       </c>
       <c r="I5" t="n">
         <v>297.690955626607</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>37</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>10.65</v>
+        <v>3.77</v>
       </c>
       <c r="L5" t="n">
         <v>7.99</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>19.4</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44715.38541666666</v>
+        <v>44715.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>264.6</v>
+        <v>261</v>
       </c>
       <c r="I6" t="n">
         <v>263.0489086627292</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.35</v>
+        <v>-17.48</v>
       </c>
       <c r="L6" t="n">
         <v>18.81</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.04</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44753.38541666666</v>
+        <v>44753.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>220.65</v>
+        <v>230</v>
       </c>
       <c r="I7" t="n">
         <v>223.3553957216466</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K7" t="n">
-        <v>15.46</v>
+        <v>11.88</v>
       </c>
       <c r="L7" t="n">
         <v>1.67</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.23</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>224.5</v>
+        <v>221.95</v>
       </c>
       <c r="I8" t="n">
         <v>222.9961539495852</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.39</v>
+        <v>-3.5</v>
       </c>
       <c r="L8" t="n">
         <v>4.65</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.49</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44774.38541666666</v>
+        <v>44774.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>243.35</v>
+        <v>245.5</v>
       </c>
       <c r="I9" t="n">
         <v>245.2317472530916</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.640000000000001</v>
+        <v>-10.61</v>
       </c>
       <c r="L9" t="n">
         <v>11.85</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>308.3</v>
+        <v>304.3</v>
       </c>
       <c r="I10" t="n">
         <v>304.6399810323174</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>25.58</v>
+        <v>23.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.43</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>320</v>
+        <v>341.75</v>
       </c>
       <c r="I11" t="n">
         <v>336.0290755111837</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.16</v>
+        <v>-12.31</v>
       </c>
       <c r="L11" t="n">
-        <v>7.72</v>
+        <v>13.7</v>
       </c>
       <c r="M11" t="n">
         <v>0.73</v>
       </c>
       <c r="N11" t="n">
-        <v>5.49</v>
+        <v>6.64</v>
       </c>
       <c r="O11" t="n">
         <v>-3.85</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>12.05</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>329</v>
+        <v>324.5</v>
       </c>
       <c r="I12" t="n">
         <v>326.5595513746475</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.73</v>
+        <v>-5.05</v>
       </c>
       <c r="L12" t="n">
-        <v>6.47</v>
+        <v>6.55</v>
       </c>
       <c r="M12" t="n">
         <v>0.55</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>292.9</v>
+        <v>324.55</v>
       </c>
       <c r="I13" t="n">
         <v>321.9599900751267</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>9.74</v>
+        <v>-0.02</v>
       </c>
       <c r="L13" t="n">
         <v>9.029999999999999</v>
@@ -1182,7 +1337,7 @@
         <v>2.54</v>
       </c>
       <c r="N13" t="n">
-        <v>5.17</v>
+        <v>13.32</v>
       </c>
       <c r="O13" t="n">
         <v>5.17</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>14.45</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>327.5</v>
+        <v>320.6</v>
       </c>
       <c r="I14" t="n">
         <v>321.7649908943514</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K14" t="n">
-        <v>0.91</v>
+        <v>-1.22</v>
       </c>
       <c r="L14" t="n">
         <v>8.130000000000001</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44923.55208333334</v>
+        <v>44924.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="I15" t="n">
         <v>285.3695755101402</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K15" t="n">
-        <v>11.73</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>2.84</v>
       </c>
       <c r="M15" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
         <v>6.96</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>10.55</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44938.55208333334</v>
+        <v>44939.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>273.85</v>
+        <v>266.95</v>
       </c>
       <c r="I16" t="n">
         <v>270.9859737506728</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.24</v>
+        <v>-7.63</v>
       </c>
       <c r="L16" t="n">
-        <v>6.26</v>
+        <v>7.98</v>
       </c>
       <c r="M16" t="n">
         <v>0.29</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44984.55208333334</v>
+        <v>44985.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>210.4</v>
+        <v>228.15</v>
       </c>
       <c r="I17" t="n">
         <v>224.8148085657749</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K17" t="n">
-        <v>21.18</v>
+        <v>14.53</v>
       </c>
       <c r="L17" t="n">
         <v>4.44</v>
@@ -1410,7 +1613,7 @@
         <v>4.55</v>
       </c>
       <c r="N17" t="n">
-        <v>4.92</v>
+        <v>11.45</v>
       </c>
       <c r="O17" t="n">
         <v>-2.14</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>13.67</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45008.55208333334</v>
+        <v>45009.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>247.5</v>
+        <v>240.65</v>
       </c>
       <c r="I18" t="n">
         <v>245.4692505948655</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K18" t="n">
-        <v>8.48</v>
+        <v>5.48</v>
       </c>
       <c r="L18" t="n">
         <v>8.77</v>
@@ -1467,7 +1682,7 @@
         <v>1.71</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="O18" t="n">
         <v>11.45</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>10.78</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>237</v>
+        <v>244.6</v>
       </c>
       <c r="I19" t="n">
         <v>244.3308670174973</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>1.52</v>
+        <v>-1.64</v>
       </c>
       <c r="L19" t="n">
-        <v>3.66</v>
+        <v>4.05</v>
       </c>
       <c r="M19" t="n">
-        <v>0.78</v>
+        <v>2.95</v>
       </c>
       <c r="N19" t="n">
         <v>6.76</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.23</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>248.5</v>
+        <v>246.25</v>
       </c>
       <c r="I20" t="n">
         <v>248.0908857613585</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K20" t="n">
-        <v>1.59</v>
+        <v>0.67</v>
       </c>
       <c r="L20" t="n">
         <v>2.47</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>6.55</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45070.55208333334</v>
+        <v>45071.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>249</v>
+        <v>258.45</v>
       </c>
       <c r="I21" t="n">
         <v>257.1104550583184</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.12</v>
+        <v>-4.95</v>
       </c>
       <c r="L21" t="n">
-        <v>3.86</v>
+        <v>6.52</v>
       </c>
       <c r="M21" t="n">
         <v>0.53</v>
       </c>
       <c r="N21" t="n">
-        <v>0.82</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
         <v>-1.01</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45124.55208333334</v>
+        <v>45125.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>293</v>
+        <v>286.95</v>
       </c>
       <c r="I22" t="n">
         <v>288.9083872262934</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K22" t="n">
-        <v>13.37</v>
+        <v>11.03</v>
       </c>
       <c r="L22" t="n">
         <v>4.02</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45146.55208333334</v>
+        <v>45147.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>290.85</v>
+        <v>306.15</v>
       </c>
       <c r="I23" t="n">
         <v>305.6687319322736</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.36</v>
+        <v>-6.69</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>7.25</v>
       </c>
       <c r="M23" t="n">
         <v>0.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.77</v>
+        <v>8.82</v>
       </c>
       <c r="O23" t="n">
         <v>-1.37</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.6</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>397.45</v>
+        <v>394.65</v>
       </c>
       <c r="I24" t="n">
         <v>397.317029739351</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K24" t="n">
-        <v>29.82</v>
+        <v>28.91</v>
       </c>
       <c r="L24" t="n">
         <v>5.26</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45251.55208333334</v>
+        <v>45252.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>401.75</v>
+        <v>412.3</v>
       </c>
       <c r="I25" t="n">
         <v>406.2062362886408</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.8</v>
+        <v>-4.47</v>
       </c>
       <c r="L25" t="n">
-        <v>4.35</v>
+        <v>5.08</v>
       </c>
       <c r="M25" t="n">
         <v>5.13</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.12</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>424.8</v>
+        <v>406.5</v>
       </c>
       <c r="I26" t="n">
         <v>423.1978087837414</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>3.03</v>
+        <v>-1.41</v>
       </c>
       <c r="L26" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="M26" t="n">
         <v>4.48</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.51</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45299.55208333334</v>
+        <v>45300.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>419.45</v>
+        <v>447.1</v>
       </c>
       <c r="I27" t="n">
         <v>435.232904751058</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.19</v>
+        <v>-9.99</v>
       </c>
       <c r="L27" t="n">
-        <v>6.15</v>
+        <v>10.18</v>
       </c>
       <c r="M27" t="n">
         <v>2.56</v>
       </c>
       <c r="N27" t="n">
-        <v>3.35</v>
+        <v>8.48</v>
       </c>
       <c r="O27" t="n">
         <v>-5.77</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.03</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>503</v>
+        <v>472.4</v>
       </c>
       <c r="I28" t="n">
         <v>484.7337031171416</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K28" t="n">
-        <v>12.5</v>
+        <v>5.66</v>
       </c>
       <c r="L28" t="n">
         <v>6.04</v>
@@ -2037,7 +2372,7 @@
         <v>2.69</v>
       </c>
       <c r="N28" t="n">
-        <v>4.9</v>
+        <v>7.81</v>
       </c>
       <c r="O28" t="n">
         <v>8.48</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>13.89</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>512</v>
+        <v>521.65</v>
       </c>
       <c r="I29" t="n">
         <v>515.5365942959527</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.380000000000001</v>
+        <v>-10.43</v>
       </c>
       <c r="L29" t="n">
         <v>11.92</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.07</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>620</v>
+        <v>582.4</v>
       </c>
       <c r="I30" t="n">
         <v>600.3558532740394</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>18.85</v>
+        <v>11.65</v>
       </c>
       <c r="L30" t="n">
         <v>1.6</v>
@@ -2151,7 +2510,7 @@
         <v>3.84</v>
       </c>
       <c r="N30" t="n">
-        <v>3.46</v>
+        <v>6.45</v>
       </c>
       <c r="O30" t="n">
         <v>0.25</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.97</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45426.38541666666</v>
+        <v>45426.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="I31" t="n">
         <v>595.938776076336</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.99</v>
+        <v>-3.02</v>
       </c>
       <c r="L31" t="n">
         <v>6.57</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>11.36</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>659.95</v>
+        <v>560.4</v>
       </c>
       <c r="I32" t="n">
         <v>595.2569080672523</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>9.99</v>
+        <v>-6.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.98</v>
+        <v>12</v>
       </c>
       <c r="M32" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>3.24</v>
+        <v>14.54</v>
       </c>
       <c r="O32" t="n">
         <v>4.53</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>22.95</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>652.05</v>
+        <v>660</v>
       </c>
       <c r="I33" t="n">
         <v>652.6911544655256</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>-16.35</v>
+        <v>-17.77</v>
       </c>
       <c r="L33" t="n">
-        <v>17.95</v>
+        <v>19.35</v>
       </c>
       <c r="M33" t="n">
         <v>2.07</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.35</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>711</v>
+        <v>691.25</v>
       </c>
       <c r="I34" t="n">
         <v>694.9875906309389</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>7.73</v>
+        <v>4.73</v>
       </c>
       <c r="L34" t="n">
         <v>1.64</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.1</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45504.55208333334</v>
+        <v>45505.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>727.9</v>
+        <v>733.3</v>
       </c>
       <c r="I35" t="n">
         <v>730.1634393123813</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.3</v>
+        <v>-6.08</v>
       </c>
       <c r="L35" t="n">
-        <v>5.89</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>2.14</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.52</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>722.85</v>
+        <v>683.7</v>
       </c>
       <c r="I36" t="n">
         <v>685.4595992203255</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.43</v>
+        <v>-6.76</v>
       </c>
       <c r="L36" t="n">
-        <v>3.04</v>
+        <v>7.81</v>
       </c>
       <c r="M36" t="n">
-        <v>0.06</v>
+        <v>4.41</v>
       </c>
       <c r="N36" t="n">
-        <v>1.22</v>
+        <v>5.44</v>
       </c>
       <c r="O36" t="n">
         <v>0.54</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45524.38541666666</v>
+        <v>45524.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>696.95</v>
+        <v>709</v>
       </c>
       <c r="I37" t="n">
         <v>701.3625069682226</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.94</v>
+        <v>-3.7</v>
       </c>
       <c r="L37" t="n">
         <v>5.02</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>7.83</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>693.5</v>
+        <v>690.55</v>
       </c>
       <c r="I38" t="n">
         <v>691.0577360295084</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.19</v>
+        <v>-2.6</v>
       </c>
       <c r="L38" t="n">
-        <v>2.57</v>
+        <v>4.62</v>
       </c>
       <c r="M38" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="N38" t="n">
         <v>2.23</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.86</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>709</v>
+        <v>732.45</v>
       </c>
       <c r="I39" t="n">
         <v>731.002998120365</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.67</v>
+        <v>-6.07</v>
       </c>
       <c r="L39" t="n">
-        <v>4.84</v>
+        <v>8.08</v>
       </c>
       <c r="M39" t="n">
         <v>0.58</v>
       </c>
       <c r="N39" t="n">
-        <v>2.88</v>
+        <v>3.31</v>
       </c>
       <c r="O39" t="n">
         <v>0.22</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.4</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45562.38541666666</v>
+        <v>45562.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>763.25</v>
+        <v>733.7</v>
       </c>
       <c r="I40" t="n">
         <v>737.2719395361082</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>4.21</v>
+        <v>0.17</v>
       </c>
       <c r="L40" t="n">
         <v>3.73</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>721</v>
+        <v>733.3</v>
       </c>
       <c r="I41" t="n">
         <v>722.4839434082066</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>1.73</v>
+        <v>0.05</v>
       </c>
       <c r="L41" t="n">
         <v>4.11</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45582.55208333334</v>
+        <v>45583.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>678.95</v>
+        <v>675.7</v>
       </c>
       <c r="I42" t="n">
         <v>676.626042256888</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.41</v>
+        <v>-7.85</v>
       </c>
       <c r="L42" t="n">
-        <v>7.95</v>
+        <v>9.16</v>
       </c>
       <c r="M42" t="n">
         <v>0.13</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.23</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45602.55208333334</v>
+        <v>45603.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>684.95</v>
+        <v>716.25</v>
       </c>
       <c r="I43" t="n">
         <v>703.0065367184873</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.37</v>
+        <v>-6</v>
       </c>
       <c r="L43" t="n">
-        <v>3.18</v>
+        <v>6.83</v>
       </c>
       <c r="M43" t="n">
         <v>0.91</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>9.5</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45615.55208333334</v>
+        <v>45617.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>708.5</v>
+        <v>687.25</v>
       </c>
       <c r="I44" t="n">
         <v>697.4739048760021</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.08</v>
+        <v>-4.05</v>
       </c>
       <c r="L44" t="n">
-        <v>4.06</v>
+        <v>4.64</v>
       </c>
       <c r="M44" t="n">
-        <v>0.29</v>
+        <v>0.64</v>
       </c>
       <c r="N44" t="n">
         <v>2.83</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.91</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45639.55208333334</v>
+        <v>45642.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>678</v>
+        <v>687.85</v>
       </c>
       <c r="I45" t="n">
         <v>687.6831749984964</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K45" t="n">
-        <v>1.35</v>
+        <v>-0.09</v>
       </c>
       <c r="L45" t="n">
         <v>3.53</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>5.05</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45649.55208333334</v>
+        <v>45650.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>659.8</v>
+        <v>646.2</v>
       </c>
       <c r="I46" t="n">
         <v>653.1329661222959</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.08</v>
+        <v>-6.06</v>
       </c>
       <c r="L46" t="n">
-        <v>4.63</v>
+        <v>6.08</v>
       </c>
       <c r="M46" t="n">
         <v>1.62</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.56</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>562.8</v>
+        <v>570.4</v>
       </c>
       <c r="I47" t="n">
         <v>568.4566777772233</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
-        <v>12.91</v>
+        <v>11.73</v>
       </c>
       <c r="L47" t="n">
         <v>4.3</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>544.55</v>
+        <v>539</v>
       </c>
       <c r="I48" t="n">
         <v>539.2568612435595</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.53</v>
+        <v>-5.5</v>
       </c>
       <c r="L48" t="n">
-        <v>5.66</v>
+        <v>7.08</v>
       </c>
       <c r="M48" t="n">
         <v>0.91</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.12</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>454.7</v>
+        <v>473.75</v>
       </c>
       <c r="I49" t="n">
         <v>469.7305634030476</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>15.64</v>
+        <v>12.11</v>
       </c>
       <c r="L49" t="n">
         <v>0.61</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>12.09</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>458.55</v>
+        <v>444.9</v>
       </c>
       <c r="I50" t="n">
         <v>445.766136839162</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.21</v>
+        <v>-6.09</v>
       </c>
       <c r="L50" t="n">
-        <v>5.27</v>
+        <v>6.63</v>
       </c>
       <c r="M50" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="N50" t="n">
         <v>3.22</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>10.95</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>481.4</v>
+        <v>501.15</v>
       </c>
       <c r="I51" t="n">
         <v>493.634434392353</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.64</v>
       </c>
       <c r="L51" t="n">
-        <v>9.09</v>
+        <v>13.05</v>
       </c>
       <c r="M51" t="n">
         <v>0.43</v>
       </c>
       <c r="N51" t="n">
-        <v>2.51</v>
+        <v>5.72</v>
       </c>
       <c r="O51" t="n">
         <v>0.91</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>12.01</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>536.85</v>
+        <v>524</v>
       </c>
       <c r="I52" t="n">
         <v>528.5327002280584</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K52" t="n">
-        <v>7.12</v>
+        <v>4.56</v>
       </c>
       <c r="L52" t="n">
         <v>4.37</v>
       </c>
       <c r="M52" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="N52" t="n">
         <v>4.03</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>488</v>
+        <v>501.05</v>
       </c>
       <c r="I53" t="n">
         <v>491.1325442031057</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K53" t="n">
-        <v>6.87</v>
+        <v>4.38</v>
       </c>
       <c r="L53" t="n">
         <v>3.22</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>8.35</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>517.8</v>
+        <v>508.75</v>
       </c>
       <c r="I54" t="n">
         <v>512.5546461268648</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>3.34</v>
+        <v>1.54</v>
       </c>
       <c r="L54" t="n">
         <v>3.83</v>
       </c>
       <c r="M54" t="n">
-        <v>0.28</v>
+        <v>2.99</v>
       </c>
       <c r="N54" t="n">
         <v>3.49</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.19</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45834.38541666666</v>
+        <v>45834.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>510.2</v>
+        <v>517.35</v>
       </c>
       <c r="I55" t="n">
         <v>513.0176768770801</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.29</v>
+        <v>-1.69</v>
       </c>
       <c r="L55" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="M55" t="n">
         <v>1.34</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.98</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>513.05</v>
+        <v>502.9</v>
       </c>
       <c r="I56" t="n">
         <v>512.3744316101088</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>61</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.83</v>
+        <v>-2.79</v>
       </c>
       <c r="L56" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="M56" t="n">
         <v>1.14</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>5.43</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>504.2</v>
+        <v>514.45</v>
       </c>
       <c r="I57" t="n">
         <v>512.4599535939964</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.26</v>
+        <v>-2.3</v>
       </c>
       <c r="L57" t="n">
-        <v>2.51</v>
+        <v>3.4</v>
       </c>
       <c r="M57" t="n">
         <v>0.42</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>4.95</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>528.7</v>
+        <v>521.75</v>
       </c>
       <c r="I58" t="n">
         <v>523.1671195141686</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
-        <v>2.77</v>
+        <v>1.42</v>
       </c>
       <c r="L58" t="n">
         <v>1.84</v>
       </c>
       <c r="M58" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="N58" t="n">
         <v>1.42</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>5.43</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45936.55208333334</v>
+        <v>45937.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>541.5</v>
+        <v>554.25</v>
       </c>
       <c r="I59" t="n">
         <v>547.0315688744437</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.79</v>
+        <v>-6.23</v>
       </c>
       <c r="L59" t="n">
-        <v>4.03</v>
+        <v>6.83</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.68</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45947.55208333334</v>
+        <v>45950.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>540.95</v>
+        <v>525</v>
       </c>
       <c r="I60" t="n">
         <v>527.4257776356421</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.4</v>
+        <v>-5.28</v>
       </c>
       <c r="L60" t="n">
-        <v>4.36</v>
+        <v>7.26</v>
       </c>
       <c r="M60" t="n">
         <v>0.55</v>
       </c>
       <c r="N60" t="n">
-        <v>2.29</v>
+        <v>2.95</v>
       </c>
       <c r="O60" t="n">
         <v>1.14</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.82</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46003.38541666666</v>
+        <v>46003.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>465.35</v>
+        <v>483</v>
       </c>
       <c r="I61" t="n">
         <v>479.4158241856548</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K61" t="n">
-        <v>11.36</v>
+        <v>8</v>
       </c>
       <c r="L61" t="n">
         <v>4.07</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.57</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>497</v>
+        <v>491.15</v>
       </c>
       <c r="I62" t="n">
         <v>493.7340360234972</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>2.9</v>
+        <v>1.69</v>
       </c>
       <c r="L62" t="n">
         <v>3.87</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.05</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>472</v>
+        <v>477.55</v>
       </c>
       <c r="I63" t="n">
         <v>477.2042815926964</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K63" t="n">
-        <v>3.9</v>
+        <v>2.77</v>
       </c>
       <c r="L63" t="n">
         <v>2.55</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.1</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>483</v>
+        <v>470.75</v>
       </c>
       <c r="I64" t="n">
         <v>471.23935658444</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K64" t="n">
-        <v>1.14</v>
+        <v>-1.42</v>
       </c>
       <c r="L64" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="M64" t="n">
         <v>3.61</v>
       </c>
       <c r="N64" t="n">
-        <v>2.35</v>
+        <v>3.43</v>
       </c>
       <c r="O64" t="n">
         <v>1.69</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.12</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46092.55208333334</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>487.65</v>
+        <v>523.6</v>
       </c>
       <c r="I65" t="n">
         <v>500.6062990974087</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.59</v>
+        <v>-11.23</v>
       </c>
       <c r="L65" t="n">
-        <v>6.11</v>
+        <v>12.16</v>
       </c>
       <c r="M65" t="n">
         <v>0.74</v>
       </c>
       <c r="N65" t="n">
-        <v>3.31</v>
+        <v>6.43</v>
       </c>
       <c r="O65" t="n">
         <v>-3.43</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>11.69</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46108.55208333334</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>482</v>
+        <v>475.05</v>
       </c>
       <c r="I66" t="n">
         <v>480.2458897940014</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K66" t="n">
-        <v>-7.94</v>
+        <v>-9.27</v>
       </c>
       <c r="L66" t="n">
-        <v>8.33</v>
+        <v>10.05</v>
       </c>
       <c r="M66" t="n">
-        <v>0.75</v>
+        <v>1.18</v>
       </c>
       <c r="N66" t="n">
         <v>4.76</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>7.99</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46122.55208333334</v>
+        <v>46125.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>487.95</v>
+        <v>510</v>
       </c>
       <c r="I67" t="n">
         <v>507.4369231961874</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.72</v>
+        <v>-7.36</v>
       </c>
       <c r="L67" t="n">
-        <v>6.92</v>
+        <v>7.48</v>
       </c>
       <c r="M67" t="n">
         <v>3.2</v>
       </c>
       <c r="N67" t="n">
-        <v>3.31</v>
+        <v>5.44</v>
       </c>
       <c r="O67" t="n">
         <v>-2.07</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>11.65</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>558</v>
+        <v>523.9</v>
       </c>
       <c r="I68" t="n">
         <v>545.8010594584714</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K68" t="n">
-        <v>9.41</v>
+        <v>2.73</v>
       </c>
       <c r="L68" t="n">
         <v>7.36</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.27</v>
       </c>
       <c r="N68" t="n">
-        <v>3.81</v>
+        <v>6.76</v>
       </c>
       <c r="O68" t="n">
         <v>5.44</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>551.5</v>
+        <v>554.45</v>
       </c>
       <c r="I69" t="n">
         <v>551.993030844208</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K69" t="n">
-        <v>-5.27</v>
+        <v>-5.83</v>
       </c>
       <c r="L69" t="n">
-        <v>5.71</v>
+        <v>6.67</v>
       </c>
       <c r="M69" t="n">
         <v>1.49</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.07</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>580.3</v>
+        <v>564.7</v>
       </c>
       <c r="I70" t="n">
         <v>566.0632673583472</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>4.66</v>
+        <v>1.85</v>
       </c>
       <c r="L70" t="n">
         <v>0.51</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46223.38541666666</v>
+        <v>46223.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>564.25</v>
+        <v>566.3</v>
       </c>
       <c r="I71" t="n">
         <v>564.5049640896729</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K71" t="n">
-        <v>0.08</v>
+        <v>-0.28</v>
       </c>
       <c r="L71" t="n">
         <v>4.83</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>5.28</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>555.3</v>
+        <v>551.1</v>
       </c>
       <c r="I72" t="n">
         <v>551.865928480638</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.94</v>
+        <v>-2.68</v>
       </c>
       <c r="L72" t="n">
         <v>4.64</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.24</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>462.2</v>
+        <v>486.5</v>
       </c>
       <c r="I73" t="n">
         <v>485.1962751562357</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K73" t="n">
-        <v>16.13</v>
+        <v>11.72</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
@@ -4602,7 +5477,7 @@
         <v>0.97</v>
       </c>
       <c r="N73" t="n">
-        <v>3.91</v>
+        <v>5.8</v>
       </c>
       <c r="O73" t="n">
         <v>-1.26</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>8.73</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>464.2</v>
+        <v>440.4</v>
       </c>
       <c r="I74" t="n">
         <v>458.9975171234491</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.58</v>
+        <v>-9.48</v>
       </c>
       <c r="L74" t="n">
-        <v>5.33</v>
+        <v>9.48</v>
       </c>
       <c r="M74" t="n">
         <v>0.75</v>
       </c>
       <c r="N74" t="n">
-        <v>2.26</v>
+        <v>4.02</v>
       </c>
       <c r="O74" t="n">
         <v>5.8</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,12 @@
       <c r="Q75" t="n">
         <v>6</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6821,7 +7726,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="6">
@@ -6831,7 +7736,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7">
@@ -6841,7 +7746,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -6851,7 +7756,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6861,7 +7766,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -6871,7 +7776,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -6881,7 +7786,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -6891,7 +7796,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6901,7 +7806,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6911,7 +7816,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.18</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="15">
@@ -6921,7 +7826,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.82</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="16">
@@ -6931,7 +7836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.53</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="17">
@@ -6941,7 +7846,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.82</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="18">
@@ -6951,7 +7856,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="19">
@@ -6961,7 +7866,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.17</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="20">
@@ -6971,7 +7876,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.37</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="21">
@@ -6981,7 +7886,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.81</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="22">
@@ -6991,7 +7896,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -7001,7 +7906,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -7011,7 +7916,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="25">
@@ -7031,7 +7936,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.18</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="27">
@@ -7041,7 +7946,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.18</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="28">
@@ -7051,7 +7956,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
